--- a/4310.1 карта регистров.xlsx
+++ b/4310.1 карта регистров.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpaceVDK\В работе\4310_1 Флотатор\Карта регистров\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpaceVDK\GIT\Flotator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CE801B-E391-4486-8ED7-E028F54093B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0EE314-4274-4B8D-98F1-2A8E5A65BDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF20929-9022-43B0-A2B6-5A527A11B739}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF20929-9022-43B0-A2B6-5A527A11B739}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="693">
   <si>
     <t>REAL</t>
   </si>
@@ -2108,6 +2108,15 @@
   </si>
   <si>
     <t>Задвижка XYV 1</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>D501.5</t>
+  </si>
+  <si>
+    <t>Авария запрет открытия задвижек</t>
   </si>
 </sst>
 </file>
@@ -2734,25 +2743,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8DCC9E-C7CA-49A6-AF37-3F9B9D79926B}">
-  <dimension ref="B1:L83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:L84"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
-    <col min="7" max="7" width="39.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="19.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="9.109375" style="1"/>
+    <col min="7" max="7" width="39.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="1"/>
+    <col min="10" max="10" width="19.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B1" s="9" t="s">
         <v>516</v>
       </c>
@@ -2775,7 +2784,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
         <v>572</v>
       </c>
@@ -2786,7 +2795,7 @@
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>622</v>
       </c>
@@ -3014,7 +3023,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>628</v>
       </c>
@@ -3680,7 +3689,7 @@
       <c r="G45" s="19"/>
       <c r="H45" s="19"/>
     </row>
-    <row r="46" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
         <v>651</v>
       </c>
@@ -3703,7 +3712,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
         <v>652</v>
       </c>
@@ -3726,7 +3735,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
         <v>653</v>
       </c>
@@ -3749,7 +3758,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="49" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
         <v>654</v>
       </c>
@@ -3772,7 +3781,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="50" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
         <v>655</v>
       </c>
@@ -3795,7 +3804,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="51" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
         <v>656</v>
       </c>
@@ -3818,7 +3827,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="52" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
         <v>657</v>
       </c>
@@ -3841,7 +3850,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="53" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
         <v>658</v>
       </c>
@@ -3864,7 +3873,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="54" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
         <v>659</v>
       </c>
@@ -3887,7 +3896,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="55" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B55" s="2" t="s">
         <v>660</v>
       </c>
@@ -3910,7 +3919,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="56" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
         <v>661</v>
       </c>
@@ -3933,7 +3942,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="57" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
         <v>662</v>
       </c>
@@ -3956,7 +3965,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="58" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
         <v>663</v>
       </c>
@@ -3979,7 +3988,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="59" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
         <v>664</v>
       </c>
@@ -4002,7 +4011,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="60" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
         <v>665</v>
       </c>
@@ -4025,7 +4034,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="61" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
         <v>666</v>
       </c>
@@ -4048,7 +4057,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="62" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
         <v>667</v>
       </c>
@@ -4071,7 +4080,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="63" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
         <v>668</v>
       </c>
@@ -4094,7 +4103,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B64" s="2" t="s">
         <v>669</v>
       </c>
@@ -4117,7 +4126,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="65" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B65" s="2" t="s">
         <v>670</v>
       </c>
@@ -4140,7 +4149,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="66" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B66" s="2" t="s">
         <v>671</v>
       </c>
@@ -4163,7 +4172,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="67" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B67" s="2" t="s">
         <v>672</v>
       </c>
@@ -4186,7 +4195,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="68" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B68" s="2" t="s">
         <v>673</v>
       </c>
@@ -4542,18 +4551,41 @@
         <v>522</v>
       </c>
     </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:J8"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="B35:H35"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:J8"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4564,16 +4596,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3859C396-C82A-4DAD-8EB4-D7F27E594D01}">
   <dimension ref="A1:L203"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="47.85546875" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="2" max="2" width="47.88671875" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="9" max="9" width="29.7109375" customWidth="1"/>
-    <col min="11" max="11" width="28.28515625" customWidth="1"/>
+    <col min="9" max="9" width="29.6640625" customWidth="1"/>
+    <col min="11" max="11" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -4590,7 +4622,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4604,7 +4636,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -4618,7 +4650,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>50</v>
       </c>
@@ -4632,7 +4664,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>52</v>
       </c>
@@ -4646,7 +4678,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>54</v>
       </c>
@@ -4660,7 +4692,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>56</v>
       </c>
@@ -4674,7 +4706,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>58</v>
       </c>
@@ -4688,7 +4720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>60</v>
       </c>
@@ -4702,7 +4734,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>63</v>
       </c>
@@ -4716,7 +4748,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>66</v>
       </c>
@@ -4730,7 +4762,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>69</v>
       </c>
@@ -4756,7 +4788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>71</v>
       </c>
@@ -4782,7 +4814,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>74</v>
       </c>
@@ -4808,7 +4840,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>77</v>
       </c>
@@ -4834,7 +4866,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>80</v>
       </c>
@@ -4860,7 +4892,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>83</v>
       </c>
@@ -4886,7 +4918,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>86</v>
       </c>
@@ -4900,7 +4932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>89</v>
       </c>
@@ -4914,7 +4946,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4928,7 +4960,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>96</v>
       </c>
@@ -4942,7 +4974,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>99</v>
       </c>
@@ -4956,7 +4988,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>102</v>
       </c>
@@ -4970,7 +5002,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>105</v>
       </c>
@@ -4984,7 +5016,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>108</v>
       </c>
@@ -4998,7 +5030,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>111</v>
       </c>
@@ -5012,7 +5044,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>114</v>
       </c>
@@ -5026,7 +5058,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>117</v>
       </c>
@@ -5040,7 +5072,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>120</v>
       </c>
@@ -5054,7 +5086,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>123</v>
       </c>
@@ -5068,7 +5100,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>126</v>
       </c>
@@ -5082,7 +5114,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>129</v>
       </c>
@@ -5096,7 +5128,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>132</v>
       </c>
@@ -5110,7 +5142,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>135</v>
       </c>
@@ -5124,7 +5156,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>137</v>
       </c>
@@ -5138,7 +5170,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>140</v>
       </c>
@@ -5152,7 +5184,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>143</v>
       </c>
@@ -5166,7 +5198,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>146</v>
       </c>
@@ -5180,7 +5212,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>149</v>
       </c>
@@ -5194,7 +5226,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>152</v>
       </c>
@@ -5208,7 +5240,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>155</v>
       </c>
@@ -5222,7 +5254,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>158</v>
       </c>
@@ -5236,7 +5268,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -5250,7 +5282,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -5264,7 +5296,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>5</v>
       </c>
@@ -5275,7 +5307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>6</v>
       </c>
@@ -5296,7 +5328,7 @@
       <c r="K46" s="26"/>
       <c r="L46" s="26"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>169</v>
       </c>
@@ -5310,7 +5342,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>171</v>
       </c>
@@ -5324,7 +5356,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>173</v>
       </c>
@@ -5338,7 +5370,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>175</v>
       </c>
@@ -5352,7 +5384,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
         <v>177</v>
       </c>
@@ -5366,7 +5398,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>179</v>
       </c>
@@ -5380,7 +5412,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>181</v>
       </c>
@@ -5406,7 +5438,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>183</v>
       </c>
@@ -5432,7 +5464,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>185</v>
       </c>
@@ -5458,7 +5490,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
         <v>187</v>
       </c>
@@ -5484,7 +5516,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>7</v>
       </c>
@@ -5510,7 +5542,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>192</v>
       </c>
@@ -5530,7 +5562,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
         <v>194</v>
       </c>
@@ -5544,7 +5576,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
         <v>196</v>
       </c>
@@ -5558,7 +5590,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>198</v>
       </c>
@@ -5572,7 +5604,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>200</v>
       </c>
@@ -5586,7 +5618,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>202</v>
       </c>
@@ -5600,7 +5632,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>204</v>
       </c>
@@ -5614,7 +5646,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>206</v>
       </c>
@@ -5628,7 +5660,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>208</v>
       </c>
@@ -5642,7 +5674,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>210</v>
       </c>
@@ -5656,7 +5688,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>212</v>
       </c>
@@ -5670,7 +5702,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>214</v>
       </c>
@@ -5684,7 +5716,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>216</v>
       </c>
@@ -5698,7 +5730,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>218</v>
       </c>
@@ -5712,7 +5744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>219</v>
       </c>
@@ -5726,7 +5758,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>221</v>
       </c>
@@ -5740,7 +5772,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>223</v>
       </c>
@@ -5754,7 +5786,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>225</v>
       </c>
@@ -5768,7 +5800,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>227</v>
       </c>
@@ -5782,7 +5814,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>8</v>
       </c>
@@ -5796,7 +5828,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>9</v>
       </c>
@@ -5816,7 +5848,7 @@
       <c r="K78" s="26"/>
       <c r="L78" s="26"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>10</v>
       </c>
@@ -5830,7 +5862,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
         <v>235</v>
       </c>
@@ -5856,7 +5888,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
         <v>237</v>
       </c>
@@ -5882,7 +5914,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
         <v>239</v>
       </c>
@@ -5908,7 +5940,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B83" t="s">
         <v>241</v>
       </c>
@@ -5928,7 +5960,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
         <v>243</v>
       </c>
@@ -5942,7 +5974,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
         <v>245</v>
       </c>
@@ -5956,7 +5988,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B86" t="s">
         <v>247</v>
       </c>
@@ -5970,7 +6002,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B87" t="s">
         <v>249</v>
       </c>
@@ -5984,7 +6016,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B88" t="s">
         <v>251</v>
       </c>
@@ -5998,7 +6030,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B89" t="s">
         <v>253</v>
       </c>
@@ -6012,7 +6044,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>11</v>
       </c>
@@ -6026,7 +6058,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B91" t="s">
         <v>257</v>
       </c>
@@ -6040,7 +6072,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B92" t="s">
         <v>259</v>
       </c>
@@ -6054,7 +6086,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B93" t="s">
         <v>261</v>
       </c>
@@ -6068,7 +6100,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B94" t="s">
         <v>263</v>
       </c>
@@ -6082,7 +6114,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B95" t="s">
         <v>265</v>
       </c>
@@ -6096,7 +6128,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B96" t="s">
         <v>267</v>
       </c>
@@ -6110,7 +6142,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>269</v>
       </c>
@@ -6124,7 +6156,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>271</v>
       </c>
@@ -6138,7 +6170,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>273</v>
       </c>
@@ -6152,7 +6184,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>275</v>
       </c>
@@ -6166,7 +6198,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>277</v>
       </c>
@@ -6180,7 +6212,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>279</v>
       </c>
@@ -6194,7 +6226,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>281</v>
       </c>
@@ -6208,7 +6240,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>283</v>
       </c>
@@ -6222,7 +6254,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>284</v>
       </c>
@@ -6236,7 +6268,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>286</v>
       </c>
@@ -6250,7 +6282,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>288</v>
       </c>
@@ -6264,7 +6296,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>290</v>
       </c>
@@ -6278,7 +6310,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>292</v>
       </c>
@@ -6292,7 +6324,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>12</v>
       </c>
@@ -6306,7 +6338,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>13</v>
       </c>
@@ -6320,7 +6352,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>14</v>
       </c>
@@ -6331,7 +6363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>15</v>
       </c>
@@ -6342,7 +6374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>16</v>
       </c>
@@ -6353,7 +6385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>17</v>
       </c>
@@ -6367,7 +6399,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>304</v>
       </c>
@@ -6381,7 +6413,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>306</v>
       </c>
@@ -6395,7 +6427,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>308</v>
       </c>
@@ -6421,7 +6453,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>310</v>
       </c>
@@ -6447,7 +6479,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>312</v>
       </c>
@@ -6473,7 +6505,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>314</v>
       </c>
@@ -6499,7 +6531,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>316</v>
       </c>
@@ -6525,7 +6557,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>318</v>
       </c>
@@ -6551,7 +6583,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>320</v>
       </c>
@@ -6577,7 +6609,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>322</v>
       </c>
@@ -6603,7 +6635,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>325</v>
       </c>
@@ -6629,7 +6661,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>327</v>
       </c>
@@ -6643,7 +6675,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>329</v>
       </c>
@@ -6657,7 +6689,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>332</v>
       </c>
@@ -6671,7 +6703,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>18</v>
       </c>
@@ -6685,7 +6717,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>338</v>
       </c>
@@ -6699,7 +6731,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>340</v>
       </c>
@@ -6713,7 +6745,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B133" t="s">
         <v>342</v>
       </c>
@@ -6727,7 +6759,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B134" t="s">
         <v>344</v>
       </c>
@@ -6741,7 +6773,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B135" t="s">
         <v>346</v>
       </c>
@@ -6755,7 +6787,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B136" t="s">
         <v>348</v>
       </c>
@@ -6769,7 +6801,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B137" t="s">
         <v>350</v>
       </c>
@@ -6783,7 +6815,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B138" t="s">
         <v>352</v>
       </c>
@@ -6797,7 +6829,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B139" t="s">
         <v>355</v>
       </c>
@@ -6811,7 +6843,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B140" t="s">
         <v>357</v>
       </c>
@@ -6825,7 +6857,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
         <v>359</v>
       </c>
@@ -6839,7 +6871,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
         <v>362</v>
       </c>
@@ -6853,7 +6885,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
         <v>365</v>
       </c>
@@ -6867,7 +6899,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
         <v>368</v>
       </c>
@@ -6881,7 +6913,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>370</v>
       </c>
@@ -6895,7 +6927,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>372</v>
       </c>
@@ -6909,7 +6941,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>374</v>
       </c>
@@ -6923,7 +6955,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>376</v>
       </c>
@@ -6937,7 +6969,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
         <v>378</v>
       </c>
@@ -6951,7 +6983,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
         <v>381</v>
       </c>
@@ -6965,7 +6997,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
         <v>384</v>
       </c>
@@ -6979,7 +7011,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
         <v>387</v>
       </c>
@@ -6993,7 +7025,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
         <v>390</v>
       </c>
@@ -7007,7 +7039,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>19</v>
       </c>
@@ -7021,7 +7053,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>20</v>
       </c>
@@ -7035,7 +7067,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>21</v>
       </c>
@@ -7049,7 +7081,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>22</v>
       </c>
@@ -7060,7 +7092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>23</v>
       </c>
@@ -7071,7 +7103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>24</v>
       </c>
@@ -7085,7 +7117,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B160" t="s">
         <v>402</v>
       </c>
@@ -7099,7 +7131,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B161" t="s">
         <v>404</v>
       </c>
@@ -7113,7 +7145,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B162" t="s">
         <v>406</v>
       </c>
@@ -7127,7 +7159,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
         <v>408</v>
       </c>
@@ -7153,7 +7185,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
         <v>410</v>
       </c>
@@ -7179,7 +7211,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
         <v>412</v>
       </c>
@@ -7205,7 +7237,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B166" t="s">
         <v>414</v>
       </c>
@@ -7231,7 +7263,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B167" t="s">
         <v>416</v>
       </c>
@@ -7257,7 +7289,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B168" t="s">
         <v>418</v>
       </c>
@@ -7283,7 +7315,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B169" t="s">
         <v>420</v>
       </c>
@@ -7309,7 +7341,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B170" t="s">
         <v>422</v>
       </c>
@@ -7335,7 +7367,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
         <v>424</v>
       </c>
@@ -7361,7 +7393,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
         <v>426</v>
       </c>
@@ -7375,7 +7407,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
         <v>428</v>
       </c>
@@ -7389,7 +7421,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>25</v>
       </c>
@@ -7403,7 +7435,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
         <v>432</v>
       </c>
@@ -7417,7 +7449,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
         <v>434</v>
       </c>
@@ -7431,7 +7463,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>436</v>
       </c>
@@ -7445,7 +7477,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>438</v>
       </c>
@@ -7459,7 +7491,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>440</v>
       </c>
@@ -7473,7 +7505,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>442</v>
       </c>
@@ -7487,7 +7519,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>444</v>
       </c>
@@ -7501,7 +7533,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>446</v>
       </c>
@@ -7515,7 +7547,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>448</v>
       </c>
@@ -7529,7 +7561,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>450</v>
       </c>
@@ -7543,7 +7575,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>452</v>
       </c>
@@ -7557,7 +7589,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>454</v>
       </c>
@@ -7571,7 +7603,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>456</v>
       </c>
@@ -7585,7 +7617,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>458</v>
       </c>
@@ -7599,7 +7631,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
         <v>460</v>
       </c>
@@ -7613,7 +7645,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
         <v>462</v>
       </c>
@@ -7627,7 +7659,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
         <v>464</v>
       </c>
@@ -7641,7 +7673,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
         <v>466</v>
       </c>
@@ -7655,7 +7687,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B193" t="s">
         <v>468</v>
       </c>
@@ -7669,7 +7701,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
         <v>470</v>
       </c>
@@ -7683,7 +7715,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
         <v>472</v>
       </c>
@@ -7697,7 +7729,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
         <v>474</v>
       </c>
@@ -7711,7 +7743,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
         <v>476</v>
       </c>
@@ -7725,7 +7757,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>26</v>
       </c>
@@ -7739,7 +7771,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>27</v>
       </c>
@@ -7753,7 +7785,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>28</v>
       </c>
@@ -7767,7 +7799,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>29</v>
       </c>
@@ -7778,7 +7810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>30</v>
       </c>
@@ -7789,7 +7821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>31</v>
       </c>

--- a/4310.1 карта регистров.xlsx
+++ b/4310.1 карта регистров.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpaceVDK\GIT\Flotator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0EE314-4274-4B8D-98F1-2A8E5A65BDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C896F359-CD3E-47ED-AA0F-856C3EBD6DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF20929-9022-43B0-A2B6-5A527A11B739}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="696">
   <si>
     <t>REAL</t>
   </si>
@@ -2116,7 +2116,16 @@
     <t>D501.5</t>
   </si>
   <si>
-    <t>Авария запрет открытия задвижек</t>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Авария запрет открытия задвижки 2</t>
+  </si>
+  <si>
+    <t>Авария запрет открытия задвижки 1</t>
+  </si>
+  <si>
+    <t>D501.6</t>
   </si>
 </sst>
 </file>
@@ -2743,7 +2752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8DCC9E-C7CA-49A6-AF37-3F9B9D79926B}">
-  <dimension ref="B1:L84"/>
+  <dimension ref="B1:L85"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="1"/>
@@ -4568,24 +4577,47 @@
         <v>691</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>524</v>
       </c>
     </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B85" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="B45:H45"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B69:H69"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:J8"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/4310.1 карта регистров.xlsx
+++ b/4310.1 карта регистров.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkSpaceVDK\GIT\Flotator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C896F359-CD3E-47ED-AA0F-856C3EBD6DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228F26A9-1869-480D-B806-33F9ECF7DC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF20929-9022-43B0-A2B6-5A527A11B739}"/>
+    <workbookView xWindow="34860" yWindow="3300" windowWidth="17280" windowHeight="8925" xr2:uid="{1AF20929-9022-43B0-A2B6-5A527A11B739}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="697">
   <si>
     <t>REAL</t>
   </si>
@@ -2126,6 +2126,9 @@
   </si>
   <si>
     <t>D501.6</t>
+  </si>
+  <si>
+    <t>фпфвп</t>
   </si>
 </sst>
 </file>
@@ -2752,7 +2755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8DCC9E-C7CA-49A6-AF37-3F9B9D79926B}">
-  <dimension ref="B1:L85"/>
+  <dimension ref="B1:L97"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="1"/>
@@ -4606,18 +4609,23 @@
         <v>524</v>
       </c>
     </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:J8"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="B28:H28"/>
     <mergeCell ref="B35:H35"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B69:H69"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:J8"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
